--- a/artfynd/A 27651-2026 artfynd.xlsx
+++ b/artfynd/A 27651-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136293926</v>
       </c>
       <c r="B2" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136293927</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136293928</v>
       </c>
       <c r="B4" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136293931</v>
       </c>
       <c r="B5" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136293932</v>
       </c>
       <c r="B6" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136293924</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136293925</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136293930</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27651-2026 artfynd.xlsx
+++ b/artfynd/A 27651-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136293926</v>
       </c>
       <c r="B2" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136293927</v>
       </c>
       <c r="B3" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136293928</v>
       </c>
       <c r="B4" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136293931</v>
       </c>
       <c r="B5" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136293932</v>
       </c>
       <c r="B6" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27651-2026 artfynd.xlsx
+++ b/artfynd/A 27651-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136293926</v>
       </c>
       <c r="B2" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136293927</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136293928</v>
       </c>
       <c r="B4" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136293931</v>
       </c>
       <c r="B5" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136293932</v>
       </c>
       <c r="B6" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136293924</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136293925</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136293930</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27651-2026 artfynd.xlsx
+++ b/artfynd/A 27651-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136293926</v>
       </c>
       <c r="B2" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136293927</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136293928</v>
       </c>
       <c r="B4" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136293931</v>
       </c>
       <c r="B5" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136293932</v>
       </c>
       <c r="B6" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>136293924</v>
       </c>
       <c r="B7" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136293925</v>
       </c>
       <c r="B8" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136293930</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27651-2026 artfynd.xlsx
+++ b/artfynd/A 27651-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136293926</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136293927</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136293928</v>
       </c>
       <c r="B4" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136293931</v>
       </c>
       <c r="B5" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136293932</v>
       </c>
       <c r="B6" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
